--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0593</v>
+        <v>16.6872</v>
       </c>
       <c r="E2" t="n">
-        <v>6.02</v>
+        <v>18.859</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03930000000000011</v>
+        <v>-2.1717</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8798</v>
+        <v>14.6919</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.9363</v>
+        <v>3.4452</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8161</v>
+        <v>11.2467</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3761</v>
+        <v>22.263</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.107</v>
+        <v>7.4445</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4831</v>
+        <v>14.8185</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4964</v>
+        <v>-7.571099999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8292</v>
+        <v>-3.9994</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3329</v>
+        <v>-3.5719</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2000999999999999</v>
+        <v>-8.178899999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4007</v>
+        <v>-16.9421</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>8.763100000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6398</v>
+        <v>-4.2531</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7853</v>
+        <v>-2.6883</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1454</v>
+        <v>-1.5647</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7397</v>
+        <v>14.4274</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2593</v>
+        <v>16.2264</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5196</v>
+        <v>-1.799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4794</v>
+        <v>6.082599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.276</v>
+        <v>6.4533</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7966</v>
+        <v>-0.3707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6087999999999998</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.2342</v>
+        <v>-2.8946</v>
       </c>
       <c r="I3" t="n">
-        <v>2.843</v>
+        <v>4.7946</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6082</v>
+        <v>3.6721</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05449999999999999</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5537</v>
+        <v>4.587899999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9994</v>
+        <v>-1.7721</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2887</v>
+        <v>-1.9789</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7108</v>
+        <v>0.2067000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.4013</v>
+        <v>-2.3368</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4012</v>
+        <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2081</v>
+        <v>1.6042</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.1891</v>
+        <v>1.7859</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0189</v>
+        <v>-0.1818</v>
       </c>
       <c r="V3" t="n">
-        <v>7.0786</v>
+        <v>2.7731</v>
       </c>
       <c r="W3" t="n">
-        <v>9.257999999999999</v>
+        <v>3.3321</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1794</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.71</v>
+        <v>3.1189</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9091</v>
+        <v>1.1119</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1991</v>
+        <v>2.0069</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.03339999999999987</v>
+        <v>2.6747</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9807999999999999</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9473</v>
+        <v>2.6716</v>
       </c>
       <c r="J4" t="n">
-        <v>3.936</v>
+        <v>5.1399</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5288999999999999</v>
+        <v>3.5593</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4071</v>
+        <v>1.5806</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9696</v>
+        <v>-2.4649</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5097</v>
+        <v>-3.5562</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4599</v>
+        <v>1.091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-8.3736</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8008</v>
+        <v>5.4526</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7636</v>
+        <v>6.4884</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0148</v>
+        <v>3.5589</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7489</v>
+        <v>2.9293</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8205</v>
+        <v>-3.1232</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9589000000000001</v>
+        <v>0.7867999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7793</v>
+        <v>-3.9101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1998</v>
+        <v>2.187499999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1998</v>
+        <v>1.2733</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.9141999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1998</v>
+        <v>0.2077</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.401999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1998</v>
+        <v>-3.1943</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1998</v>
+        <v>3.8682</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.1814</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1998</v>
+        <v>-2.3134</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-3.6605</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-2.7795</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.8810999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-11.4895</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>8.568300000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2.5312</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-2.2713</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.2598</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.4322</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>11.1659</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.7338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7995000000000001</v>
+        <v>2.1316</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5575</v>
+        <v>2.1316</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.758</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4746</v>
+        <v>2.1316</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3887</v>
+        <v>0.3079</v>
       </c>
       <c r="I6" t="n">
-        <v>1.086</v>
+        <v>1.8237</v>
       </c>
       <c r="J6" t="n">
-        <v>6.3782</v>
+        <v>2.1316</v>
       </c>
       <c r="K6" t="n">
-        <v>6.0182</v>
+        <v>0.3079</v>
       </c>
       <c r="L6" t="n">
-        <v>0.36</v>
+        <v>1.8237</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09639999999999999</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6296</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.726</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.0011</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.2018</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2007</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4652</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.721</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7441</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.1391</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0777000000000001</v>
+        <v>0.6227</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7695000000000001</v>
+        <v>-3.8682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6917</v>
+        <v>4.4911</v>
       </c>
       <c r="G7" t="n">
-        <v>3.849</v>
+        <v>-0.4610000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4139999999999999</v>
+        <v>-2.4026</v>
       </c>
       <c r="I7" t="n">
-        <v>4.263</v>
+        <v>1.9417</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9249</v>
+        <v>-0.6481</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5235000000000001</v>
+        <v>-1.4265</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4014</v>
+        <v>0.7784</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07589999999999986</v>
+        <v>0.1871</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9375</v>
+        <v>-0.9761</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8616</v>
+        <v>1.1633</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8008</v>
+        <v>-0.3895999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.4013</v>
+        <v>-2.9211</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>2.5315</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.8626</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2931</v>
+        <v>-0.5787</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3132</v>
+        <v>1.4412</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5196</v>
+        <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5196</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4690999999999999</v>
+        <v>0.1951000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0709</v>
+        <v>3.2959</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6018</v>
+        <v>-3.1009</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1453</v>
+        <v>-5.9799</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2106</v>
+        <v>-2.0971</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3559</v>
+        <v>-3.8827</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8523000000000001</v>
+        <v>0.3005</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5741</v>
+        <v>-0.5846000000000002</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7218</v>
+        <v>0.8851000000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9975999999999999</v>
+        <v>-6.2803</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6365</v>
+        <v>-1.5125</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6341</v>
+        <v>-4.7679</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-6.4264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8005</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5861</v>
+        <v>7.4276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2177</v>
+        <v>5.9133</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8038</v>
+        <v>1.5142</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.6158</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.5085</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-6.124400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7481</v>
+        <v>-0.7411</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7225</v>
+        <v>-0.7058</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0257</v>
+        <v>-0.0353</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.7163</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8579</v>
+        <v>-0.8492</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0643</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0258</v>
+        <v>-0.0247</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0387</v>
+        <v>0.0371</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8429000000000002</v>
+        <v>-0.7829000000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2225</v>
+        <v>1.5402</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0653</v>
+        <v>-2.3232</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0921</v>
+        <v>5.6083</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2708</v>
+        <v>4.998</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8212</v>
+        <v>0.6103</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01109999999999989</v>
+        <v>6.5776</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9906</v>
+        <v>5.888599999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0018</v>
+        <v>0.6890000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1032</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2802</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.823</v>
+        <v>-0.07869999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8005</v>
+        <v>-4.2843</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.401</v>
+        <v>-7.2053</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6005</v>
+        <v>2.921</v>
       </c>
       <c r="S10" t="n">
-        <v>5.0289</v>
+        <v>3.7188</v>
       </c>
       <c r="T10" t="n">
-        <v>4.0327</v>
+        <v>3.161</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9962</v>
+        <v>0.5578</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9792</v>
+        <v>-5.8258</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4204000000000001</v>
+        <v>-0.9932000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5587</v>
+        <v>-4.8326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9722000000000001</v>
+        <v>-1.337400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6608</v>
+        <v>0.8270999999999993</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6886</v>
+        <v>-2.1646</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4071</v>
+        <v>6.7385</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9914</v>
+        <v>0.2494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4155</v>
+        <v>6.4891</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4303</v>
+        <v>9.735300000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6035999999999999</v>
+        <v>1.3677</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1733</v>
+        <v>8.367599999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9767</v>
+        <v>-2.9966</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3879</v>
+        <v>-1.118</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5888000000000001</v>
+        <v>-1.8787</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001</v>
+        <v>-1.1683</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8008</v>
+        <v>-6.0369</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4007</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1046000000000001</v>
+        <v>-3.9066</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8091</v>
+        <v>-3.1509</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7045</v>
+        <v>-0.7556999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9395</v>
+        <v>-3.0012</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3793</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5602</v>
+        <v>-3.2807</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>O. STUMER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.394600000000001</v>
+        <v>-3.6932</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06910000000000061</v>
+        <v>-1.7521</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3256</v>
+        <v>-1.9411</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4838</v>
+        <v>-2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.7011</v>
+        <v>-2.6956</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2173</v>
+        <v>-0.2044</v>
       </c>
       <c r="J12" t="n">
-        <v>0.07180000000000009</v>
+        <v>-1.1659</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.063</v>
+        <v>-1.2469</v>
       </c>
       <c r="L12" t="n">
-        <v>3.1348</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.5556</v>
+        <v>-1.7342</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.638</v>
+        <v>-1.4487</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9175</v>
+        <v>-0.2855000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.0015</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>4.0011</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5298</v>
+        <v>-0.2937</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3177</v>
+        <v>0.108</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.212</v>
+        <v>-0.4016999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>5.6191</v>
+        <v>0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>6.1783</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1174</v>
+        <v>-4.657699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3986</v>
+        <v>-6.0173</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7188</v>
+        <v>1.3596</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.112299999999999</v>
+        <v>1.7974</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.1065</v>
+        <v>-0.5478</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9941000000000001</v>
+        <v>2.3451</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1889000000000001</v>
+        <v>3.1057</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1488</v>
+        <v>0.2440000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9599</v>
+        <v>2.8618</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9233</v>
+        <v>-1.3085</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.9577</v>
+        <v>-0.7918000000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03439999999999999</v>
+        <v>-0.5168</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.0012</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.2015</v>
+        <v>-6.4263</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2004</v>
+        <v>4.479</v>
       </c>
       <c r="S13" t="n">
-        <v>5.396100000000001</v>
+        <v>-3.6692</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2123</v>
+        <v>-2.6966</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1836</v>
+        <v>-0.9724</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4</v>
+        <v>-0.8385</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7794</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1795</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.013199999999999</v>
+        <v>-5.9583</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7371</v>
+        <v>-2.4616</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2761</v>
+        <v>-3.4967</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1214</v>
+        <v>-4.0656</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2791</v>
+        <v>-1.5857</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-2.4798</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9189999999999998</v>
+        <v>-2.3961</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.578</v>
+        <v>-0.5002</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.341</v>
+        <v>-1.8958</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2024</v>
+        <v>-1.6695</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2988999999999999</v>
+        <v>-1.0855</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5012000000000001</v>
+        <v>-0.5841000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.8002</v>
+        <v>-0.3895</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8003</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4323</v>
+        <v>0.4141</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0179</v>
+        <v>0.324</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4144</v>
+        <v>0.09019999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4596</v>
+        <v>-3.2806</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4596</v>
+        <v>-3.2806</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,148 +1576,226 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.211600000000001</v>
+        <v>-6.164400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6906</v>
+        <v>-2.4874</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5209</v>
+        <v>-3.6772</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.5729</v>
+        <v>-5.851</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8257</v>
+        <v>-3.4432</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7472</v>
+        <v>-2.4078</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9064</v>
+        <v>-1.55</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.518</v>
+        <v>-2.7092</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3884</v>
+        <v>1.1592</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6664</v>
+        <v>-4.301</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3076</v>
+        <v>-0.734</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3588</v>
+        <v>-3.5668</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6002</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4001</v>
+        <v>-4.2842</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0003</v>
+        <v>1.9474</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4205</v>
+        <v>5.304</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6159</v>
+        <v>3.7297</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1956</v>
+        <v>1.5744</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.6593</v>
+        <v>-3.2806</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3826</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.6593</v>
+        <v>-2.898</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>M. VIEYTES VERDU</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PUJOL MOLLERUSSA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-9.7818</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9.132400000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.6494</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-6.1373</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.4679000000000002</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-5.669499999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.7988</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-3.6448</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-5.338699999999999</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-3.314</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-2.0246</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-4.478899999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-8.958</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.479</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-2.6549</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-3.1636</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.4894</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.2985</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>PUJOL MOLLERUSSA</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.5988000000000024</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7.065799999999996</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-7.664699999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-3.388</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-19.4197</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16.032</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.5512</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-3.116</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20.6673</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-20.9392</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-16.3036</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-4.635399999999999</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-14.0042</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-40.0117</v>
-      </c>
-      <c r="R16" t="n">
-        <v>26.0076</v>
-      </c>
-      <c r="S16" t="n">
-        <v>14.3932</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8.472900000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5.920300000000001</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.399600000000001</v>
-      </c>
-      <c r="W16" t="n">
-        <v>21.0527</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-18.6531</v>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.091200000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.067499999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-11.159</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9.638999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-4.578200000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14.2172</v>
+      </c>
+      <c r="J17" t="n">
+        <v>49.591</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19.8122</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29.7789</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-39.952</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-24.3905</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-15.5622</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-27.26309999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-82.76339999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>55.49959999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8.486300000000002</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.969600000000001</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.5167</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.046400000000004</v>
+      </c>
+      <c r="W17" t="n">
+        <v>38.2704</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-31.2241</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6872</v>
+        <v>21.4368</v>
       </c>
       <c r="E2" t="n">
-        <v>18.859</v>
+        <v>21.636</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1717</v>
+        <v>-0.1994000000000002</v>
       </c>
       <c r="G2" t="n">
         <v>14.6919</v>
@@ -610,13 +610,13 @@
         <v>8.763100000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.2531</v>
+        <v>0.4964</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.6883</v>
+        <v>0.08870000000000006</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5647</v>
+        <v>0.4075</v>
       </c>
       <c r="V2" t="n">
         <v>14.4274</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6.082599999999999</v>
+        <v>5.700299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4533</v>
+        <v>3.837099999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3707</v>
+        <v>1.8632</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>0.2077</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8946</v>
+        <v>3.401999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7946</v>
+        <v>-3.1943</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6721</v>
+        <v>3.8682</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9157999999999999</v>
+        <v>6.1814</v>
       </c>
       <c r="L3" t="n">
-        <v>4.587899999999999</v>
+        <v>-2.3134</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7721</v>
+        <v>-3.6605</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9789</v>
+        <v>-2.7795</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2067000000000001</v>
+        <v>-0.8810999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1947</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3368</v>
+        <v>-11.4895</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1421</v>
+        <v>8.568300000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6042</v>
+        <v>0.9817</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7859</v>
+        <v>0.2926</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1818</v>
+        <v>0.6889000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7731</v>
+        <v>7.4322</v>
       </c>
       <c r="W3" t="n">
-        <v>3.3321</v>
+        <v>11.1659</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-3.7338</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1189</v>
+        <v>5.0094</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1119</v>
+        <v>5.2194</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0069</v>
+        <v>-0.2100000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6747</v>
+        <v>1.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003000000000000114</v>
+        <v>-2.8946</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6716</v>
+        <v>4.7946</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1399</v>
+        <v>3.6721</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5593</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5806</v>
+        <v>4.587899999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4649</v>
+        <v>-1.7721</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.5562</v>
+        <v>-1.9789</v>
       </c>
       <c r="O4" t="n">
-        <v>1.091</v>
+        <v>0.2067000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.9211</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.3736</v>
+        <v>-2.3368</v>
       </c>
       <c r="R4" t="n">
-        <v>5.4526</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>6.4884</v>
+        <v>0.5309</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5589</v>
+        <v>0.5519000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9293</v>
+        <v>-0.02109999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.1232</v>
+        <v>2.7731</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7867999999999999</v>
+        <v>3.3321</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.9101</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.187499999999999</v>
+        <v>2.210199999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2733</v>
+        <v>3.642</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9141999999999999</v>
+        <v>-1.432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2077</v>
+        <v>6.7385</v>
       </c>
       <c r="H5" t="n">
-        <v>3.401999999999999</v>
+        <v>0.2494</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1943</v>
+        <v>6.4891</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8682</v>
+        <v>9.735300000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>6.1814</v>
+        <v>1.3677</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3134</v>
+        <v>8.367599999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.6605</v>
+        <v>-2.9966</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.7795</v>
+        <v>-1.118</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8810999999999999</v>
+        <v>-1.8787</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.9211</v>
+        <v>-1.1683</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11.4895</v>
+        <v>-6.0369</v>
       </c>
       <c r="R5" t="n">
-        <v>8.568300000000001</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5312</v>
+        <v>-0.359</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.2713</v>
+        <v>-0.3359</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2598</v>
+        <v>-0.02310000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>7.4322</v>
+        <v>-3.0012</v>
       </c>
       <c r="W5" t="n">
-        <v>11.1659</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7338</v>
+        <v>-3.2807</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6227</v>
+        <v>0.7547000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8682</v>
+        <v>-3.5074</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4911</v>
+        <v>4.2622</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4610000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.5315</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8626</v>
+        <v>0.9948</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5787</v>
+        <v>-0.2177999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4412</v>
+        <v>1.2124</v>
       </c>
       <c r="V7" t="n">
         <v>0.6105</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1951000000000001</v>
+        <v>-0.05340000000000023</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2959</v>
+        <v>-1.2564</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1009</v>
+        <v>1.203</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.9799</v>
+        <v>2.6747</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0971</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8827</v>
+        <v>2.6716</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3005</v>
+        <v>5.1399</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5846000000000002</v>
+        <v>3.5593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8851000000000002</v>
+        <v>1.5806</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.2803</v>
+        <v>-2.4649</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5125</v>
+        <v>-3.5562</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.7679</v>
+        <v>1.091</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3632</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.4264</v>
+        <v>-8.3736</v>
       </c>
       <c r="R8" t="n">
-        <v>7.789400000000001</v>
+        <v>5.4526</v>
       </c>
       <c r="S8" t="n">
-        <v>7.4276</v>
+        <v>3.316</v>
       </c>
       <c r="T8" t="n">
-        <v>5.9133</v>
+        <v>1.1907</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5142</v>
+        <v>2.1254</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6158</v>
+        <v>-3.1232</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5085</v>
+        <v>0.7867999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.124400000000001</v>
+        <v>-3.9101</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7411</v>
+        <v>-0.5857</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7058</v>
+        <v>-0.6061</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0353</v>
+        <v>0.0204</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7163</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0247</v>
+        <v>0.1306</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0618</v>
+        <v>0.0378</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0371</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7829000000000002</v>
+        <v>-1.1292</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5402</v>
+        <v>-3.7006</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3232</v>
+        <v>2.5713</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6083</v>
+        <v>1.7974</v>
       </c>
       <c r="H10" t="n">
-        <v>4.998</v>
+        <v>-0.5478</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6103</v>
+        <v>2.3451</v>
       </c>
       <c r="J10" t="n">
-        <v>6.5776</v>
+        <v>3.1057</v>
       </c>
       <c r="K10" t="n">
-        <v>5.888599999999999</v>
+        <v>0.2440000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6890000000000001</v>
+        <v>2.8618</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-1.3085</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.7918000000000002</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07869999999999999</v>
+        <v>-0.5168</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.2843</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.2053</v>
+        <v>-6.4263</v>
       </c>
       <c r="R10" t="n">
-        <v>2.921</v>
+        <v>4.479</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7188</v>
+        <v>-0.1407000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>3.161</v>
+        <v>-0.3802</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5578</v>
+        <v>0.2393999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.8258</v>
+        <v>-0.8385</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9932000000000001</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.8326</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.337400000000001</v>
+        <v>-3.0202</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8270999999999993</v>
+        <v>-0.1446000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1646</v>
+        <v>-2.8755</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7385</v>
+        <v>-5.9799</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2494</v>
+        <v>-2.0971</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4891</v>
+        <v>-3.8827</v>
       </c>
       <c r="J11" t="n">
-        <v>9.735300000000001</v>
+        <v>0.3005</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3677</v>
+        <v>-0.5846000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>8.367599999999999</v>
+        <v>0.8851000000000002</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9966</v>
+        <v>-6.2803</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.118</v>
+        <v>-1.5125</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8787</v>
+        <v>-4.7679</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1683</v>
+        <v>1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.0369</v>
+        <v>-6.4264</v>
       </c>
       <c r="R11" t="n">
-        <v>4.868300000000001</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.9066</v>
+        <v>4.2124</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1509</v>
+        <v>2.4725</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7556999999999998</v>
+        <v>1.7398</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0012</v>
+        <v>-2.6158</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2795</v>
+        <v>3.5085</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2807</v>
+        <v>-6.124400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6932</v>
+        <v>-3.7975</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7521</v>
+        <v>-2.0511</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9411</v>
+        <v>-1.7464</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9</v>
@@ -1390,13 +1390,13 @@
         <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2937</v>
+        <v>-0.398</v>
       </c>
       <c r="T12" t="n">
-        <v>0.108</v>
+        <v>-0.1911</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4016999999999999</v>
+        <v>-0.207</v>
       </c>
       <c r="V12" t="n">
         <v>0.2795</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.657699999999999</v>
+        <v>-3.9203</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0173</v>
+        <v>-0.7283000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3596</v>
+        <v>-3.1919</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7974</v>
+        <v>5.6083</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5478</v>
+        <v>4.998</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3451</v>
+        <v>0.6103</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1057</v>
+        <v>6.5776</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2440000000000001</v>
+        <v>5.888599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8618</v>
+        <v>0.6890000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3085</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7918000000000002</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5168</v>
+        <v>-0.07869999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.9474</v>
+        <v>-4.2843</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.4263</v>
+        <v>-7.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>4.479</v>
+        <v>2.921</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6692</v>
+        <v>0.5813999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.6966</v>
+        <v>0.8925</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9724</v>
+        <v>-0.3111</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8385</v>
+        <v>-5.8258</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.9932000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8385</v>
+        <v>-4.8326</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.9583</v>
+        <v>-5.946700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4616</v>
+        <v>-2.4994</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4967</v>
+        <v>-3.4474</v>
       </c>
       <c r="G14" t="n">
         <v>-4.0656</v>
@@ -1546,13 +1546,13 @@
         <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4141</v>
+        <v>0.4257</v>
       </c>
       <c r="T14" t="n">
-        <v>0.324</v>
+        <v>0.2861</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09019999999999997</v>
+        <v>0.1395</v>
       </c>
       <c r="V14" t="n">
         <v>-3.2806</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.164400000000001</v>
+        <v>-6.1545</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.4874</v>
+        <v>-6.293600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6772</v>
+        <v>0.1389</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.851</v>
+        <v>-6.1373</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.4432</v>
+        <v>-0.4679000000000002</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4078</v>
+        <v>-5.669499999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.55</v>
+        <v>-0.7988</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.7092</v>
+        <v>2.846</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1592</v>
+        <v>-3.6448</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.301</v>
+        <v>-5.338699999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.734</v>
+        <v>-3.314</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.5668</v>
+        <v>-2.0246</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3368</v>
+        <v>-4.478899999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.2842</v>
+        <v>-8.958</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9474</v>
+        <v>4.479</v>
       </c>
       <c r="S15" t="n">
-        <v>5.304</v>
+        <v>0.9723999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7297</v>
+        <v>-0.3247</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5744</v>
+        <v>1.2971</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.2806</v>
+        <v>3.4894</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3826</v>
+        <v>3.788</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.898</v>
+        <v>-0.2985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.7818</v>
+        <v>-8.884499999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.132400000000001</v>
+        <v>-4.7559</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6494</v>
+        <v>-4.1287</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.1373</v>
+        <v>-5.851</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4679000000000002</v>
+        <v>-3.4432</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.669499999999999</v>
+        <v>-2.4078</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7988</v>
+        <v>-1.55</v>
       </c>
       <c r="K16" t="n">
-        <v>2.846</v>
+        <v>-2.7092</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.6448</v>
+        <v>1.1592</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.338699999999999</v>
+        <v>-4.301</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.314</v>
+        <v>-0.734</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0246</v>
+        <v>-3.5668</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.478899999999999</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.958</v>
+        <v>-4.2842</v>
       </c>
       <c r="R16" t="n">
-        <v>4.479</v>
+        <v>1.9474</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6549</v>
+        <v>2.5839</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.1636</v>
+        <v>1.461</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5086000000000001</v>
+        <v>1.123</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4894</v>
+        <v>-3.2806</v>
       </c>
       <c r="W16" t="n">
-        <v>3.788</v>
+        <v>-0.3826</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2985</v>
+        <v>-2.898</v>
       </c>
     </row>
     <row r="17">
@@ -1735,16 +1735,16 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.091200000000001</v>
+        <v>3.750999999999998</v>
       </c>
       <c r="E17" t="n">
-        <v>9.067499999999999</v>
+        <v>10.92269999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.159</v>
+        <v>-7.172300000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>9.638999999999999</v>
+        <v>9.638999999999996</v>
       </c>
       <c r="H17" t="n">
         <v>-4.578200000000001</v>
@@ -1771,25 +1771,25 @@
         <v>-15.5622</v>
       </c>
       <c r="P17" t="n">
-        <v>-27.26309999999999</v>
+        <v>-27.2631</v>
       </c>
       <c r="Q17" t="n">
         <v>-82.76339999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>55.49959999999999</v>
+        <v>55.4996</v>
       </c>
       <c r="S17" t="n">
-        <v>8.486300000000002</v>
+        <v>14.3285</v>
       </c>
       <c r="T17" t="n">
-        <v>3.969600000000001</v>
+        <v>5.8241</v>
       </c>
       <c r="U17" t="n">
-        <v>4.5167</v>
+        <v>8.503499999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>7.046400000000004</v>
+        <v>7.046400000000002</v>
       </c>
       <c r="W17" t="n">
         <v>38.2704</v>
